--- a/inst/testdata/examples_of_output/testoutput_ejam2excel_fips_counties.xlsx
+++ b/inst/testdata/examples_of_output/testoutput_ejam2excel_fips_counties.xlsx
@@ -5068,8 +5068,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="11">
-    <numFmt numFmtId="167" formatCode="#,###,###"/>
+  <numFmts count="12">
+    <numFmt numFmtId="168" formatCode="#,###,###"/>
     <numFmt numFmtId="169" formatCode="#,###,##0.0"/>
     <numFmt numFmtId="171" formatCode="#,###,##0.00"/>
     <numFmt numFmtId="172" formatCode="#,###,##0.000"/>
@@ -5078,8 +5078,9 @@
     <numFmt numFmtId="175" formatCode="#,##0.0"/>
     <numFmt numFmtId="176" formatCode="#0"/>
     <numFmt numFmtId="177" formatCode="0%"/>
-    <numFmt numFmtId="178" formatCode="#,###,###"/>
-    <numFmt numFmtId="179" formatCode="$#,##0"/>
+    <numFmt numFmtId="178" formatCode="0&quot;%&quot;"/>
+    <numFmt numFmtId="179" formatCode="#,###,###"/>
+    <numFmt numFmtId="180" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -5237,7 +5238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5309,7 +5310,7 @@
     <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -5320,6 +5321,7 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8069,7 +8071,7 @@
       <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="34" t="n">
+      <c r="F2" s="35" t="n">
         <v>182400</v>
       </c>
       <c r="G2"/>
@@ -8549,7 +8551,7 @@
       <c r="FK2" s="33" t="n">
         <v>0.516052631578947</v>
       </c>
-      <c r="FL2" s="35" t="n">
+      <c r="FL2" s="36" t="n">
         <v>33191.2670778509</v>
       </c>
       <c r="FM2" s="33" t="n">
@@ -8630,13 +8632,13 @@
       <c r="GL2" s="33" t="n">
         <v>0.208928564078605</v>
       </c>
-      <c r="GM2" s="33" t="n">
+      <c r="GM2" s="34" t="n">
         <v>6.0753360745614</v>
       </c>
-      <c r="GN2" s="27" t="n">
+      <c r="GN2" s="34" t="n">
         <v>11.3695740131579</v>
       </c>
-      <c r="GO2" s="27" t="n">
+      <c r="GO2" s="34" t="n">
         <v>6.64204002192982</v>
       </c>
       <c r="GP2" s="25" t="n">
@@ -9047,13 +9049,13 @@
       <c r="LU2" s="33" t="n">
         <v>0.195319647024096</v>
       </c>
-      <c r="LV2" s="33" t="n">
+      <c r="LV2" s="34" t="n">
         <v>5.78866112415659</v>
       </c>
-      <c r="LW2" s="25" t="n">
+      <c r="LW2" s="34" t="n">
         <v>10.3142467897866</v>
       </c>
-      <c r="LX2" s="26" t="n">
+      <c r="LX2" s="34" t="n">
         <v>6.44134924160715</v>
       </c>
       <c r="LY2" s="33" t="n">
@@ -9164,13 +9166,13 @@
       <c r="NH2" s="33" t="n">
         <v>0.200285162865808</v>
       </c>
-      <c r="NI2" s="33" t="n">
+      <c r="NI2" s="34" t="n">
         <v>5.92225392296719</v>
       </c>
-      <c r="NJ2" s="26" t="n">
+      <c r="NJ2" s="34" t="n">
         <v>10.3305278174037</v>
       </c>
-      <c r="NK2" s="26" t="n">
+      <c r="NK2" s="34" t="n">
         <v>7.00927246790299</v>
       </c>
       <c r="NL2" s="33" t="n">
@@ -10112,7 +10114,7 @@
       <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="34" t="n">
+      <c r="F3" s="35" t="n">
         <v>570567</v>
       </c>
       <c r="G3"/>
@@ -10592,7 +10594,7 @@
       <c r="FK3" s="33" t="n">
         <v>0.513540039995303</v>
       </c>
-      <c r="FL3" s="35" t="n">
+      <c r="FL3" s="36" t="n">
         <v>44730.2717123611</v>
       </c>
       <c r="FM3" s="33" t="n">
@@ -10673,13 +10675,13 @@
       <c r="GL3" s="33" t="n">
         <v>0.198062966012963</v>
       </c>
-      <c r="GM3" s="33" t="n">
+      <c r="GM3" s="34" t="n">
         <v>4.90023292619447</v>
       </c>
-      <c r="GN3" s="27" t="n">
+      <c r="GN3" s="34" t="n">
         <v>10.057212737505</v>
       </c>
-      <c r="GO3" s="27" t="n">
+      <c r="GO3" s="34" t="n">
         <v>6.08552843049107</v>
       </c>
       <c r="GP3" s="25" t="n">
@@ -11090,13 +11092,13 @@
       <c r="LU3" s="33" t="n">
         <v>0.195319647024096</v>
       </c>
-      <c r="LV3" s="33" t="n">
+      <c r="LV3" s="34" t="n">
         <v>5.78866112415659</v>
       </c>
-      <c r="LW3" s="25" t="n">
+      <c r="LW3" s="34" t="n">
         <v>10.3142467897866</v>
       </c>
-      <c r="LX3" s="26" t="n">
+      <c r="LX3" s="34" t="n">
         <v>6.44134924160715</v>
       </c>
       <c r="LY3" s="33" t="n">
@@ -11207,13 +11209,13 @@
       <c r="NH3" s="33" t="n">
         <v>0.200285162865808</v>
       </c>
-      <c r="NI3" s="33" t="n">
+      <c r="NI3" s="34" t="n">
         <v>5.92225392296719</v>
       </c>
-      <c r="NJ3" s="26" t="n">
+      <c r="NJ3" s="34" t="n">
         <v>10.3305278174037</v>
       </c>
-      <c r="NK3" s="26" t="n">
+      <c r="NK3" s="34" t="n">
         <v>7.00927246790299</v>
       </c>
       <c r="NL3" s="33" t="n">
@@ -12155,7 +12157,7 @@
       <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="34" t="n">
+      <c r="F4" s="35" t="n">
         <v>240668</v>
       </c>
       <c r="G4"/>
@@ -12635,7 +12637,7 @@
       <c r="FK4" s="33" t="n">
         <v>0.513524855817973</v>
       </c>
-      <c r="FL4" s="35" t="n">
+      <c r="FL4" s="36" t="n">
         <v>42957.8949424103</v>
       </c>
       <c r="FM4" s="33" t="n">
@@ -12716,13 +12718,13 @@
       <c r="GL4" s="33" t="n">
         <v>0.195604423553527</v>
       </c>
-      <c r="GM4" s="33" t="n">
+      <c r="GM4" s="34" t="n">
         <v>7.38413042033008</v>
       </c>
-      <c r="GN4" s="27" t="n">
+      <c r="GN4" s="34" t="n">
         <v>10.3847158741503</v>
       </c>
-      <c r="GO4" s="27" t="n">
+      <c r="GO4" s="34" t="n">
         <v>8.41058221284093</v>
       </c>
       <c r="GP4" s="25" t="n">
@@ -13133,13 +13135,13 @@
       <c r="LU4" s="33" t="n">
         <v>0.195319647024096</v>
       </c>
-      <c r="LV4" s="33" t="n">
+      <c r="LV4" s="34" t="n">
         <v>5.78866112415659</v>
       </c>
-      <c r="LW4" s="25" t="n">
+      <c r="LW4" s="34" t="n">
         <v>10.3142467897866</v>
       </c>
-      <c r="LX4" s="26" t="n">
+      <c r="LX4" s="34" t="n">
         <v>6.44134924160715</v>
       </c>
       <c r="LY4" s="33" t="n">
@@ -13250,13 +13252,13 @@
       <c r="NH4" s="33" t="n">
         <v>0.200285162865808</v>
       </c>
-      <c r="NI4" s="33" t="n">
+      <c r="NI4" s="34" t="n">
         <v>5.92225392296719</v>
       </c>
-      <c r="NJ4" s="26" t="n">
+      <c r="NJ4" s="34" t="n">
         <v>10.3305278174037</v>
       </c>
-      <c r="NK4" s="26" t="n">
+      <c r="NK4" s="34" t="n">
         <v>7.00927246790299</v>
       </c>
       <c r="NL4" s="33" t="n">
@@ -17289,7 +17291,7 @@
       <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="34" t="n">
+      <c r="F2" s="35" t="n">
         <v>993635</v>
       </c>
       <c r="G2"/>
@@ -17765,7 +17767,7 @@
       <c r="FK2" s="33" t="n">
         <v>0.513997594690203</v>
       </c>
-      <c r="FL2" s="35" t="n">
+      <c r="FL2" s="36" t="n">
         <v>42182.5984262667</v>
       </c>
       <c r="FM2" s="33" t="n">
@@ -17846,13 +17848,13 @@
       <c r="GL2" s="33" t="n">
         <v>0.199390894469503</v>
       </c>
-      <c r="GM2" s="33" t="n">
+      <c r="GM2" s="34" t="n">
         <v>5.71756872493421</v>
       </c>
-      <c r="GN2" s="27" t="n">
+      <c r="GN2" s="34" t="n">
         <v>10.3774452389459</v>
       </c>
-      <c r="GO2" s="27" t="n">
+      <c r="GO2" s="34" t="n">
         <v>6.75083687672033</v>
       </c>
       <c r="GP2" s="25" t="n">
@@ -18263,13 +18265,13 @@
       <c r="LU2" s="33" t="n">
         <v>0.195319647024096</v>
       </c>
-      <c r="LV2" s="33" t="n">
+      <c r="LV2" s="34" t="n">
         <v>5.78866112415659</v>
       </c>
-      <c r="LW2" s="25" t="n">
+      <c r="LW2" s="34" t="n">
         <v>10.3142467897866</v>
       </c>
-      <c r="LX2" s="26" t="n">
+      <c r="LX2" s="34" t="n">
         <v>6.44134924160715</v>
       </c>
       <c r="LY2" s="33" t="n">
@@ -18380,13 +18382,13 @@
       <c r="NH2" s="33" t="n">
         <v>0.200285162865808</v>
       </c>
-      <c r="NI2" s="33" t="n">
+      <c r="NI2" s="34" t="n">
         <v>5.92225392296719</v>
       </c>
-      <c r="NJ2" s="26" t="n">
+      <c r="NJ2" s="34" t="n">
         <v>10.3305278174037</v>
       </c>
-      <c r="NK2" s="26" t="n">
+      <c r="NK2" s="34" t="n">
         <v>7.00927246790299</v>
       </c>
       <c r="NL2" s="33" t="n">

--- a/inst/testdata/examples_of_output/testoutput_ejam2excel_fips_counties.xlsx
+++ b/inst/testdata/examples_of_output/testoutput_ejam2excel_fips_counties.xlsx
@@ -5069,18 +5069,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="12">
-    <numFmt numFmtId="168" formatCode="#,###,###"/>
-    <numFmt numFmtId="169" formatCode="#,###,##0.0"/>
-    <numFmt numFmtId="171" formatCode="#,###,##0.00"/>
-    <numFmt numFmtId="172" formatCode="#,###,##0.000"/>
+    <numFmt numFmtId="167" formatCode="#,###,###"/>
+    <numFmt numFmtId="168" formatCode="#,###,##0.0"/>
+    <numFmt numFmtId="170" formatCode="#,###,##0.00"/>
+    <numFmt numFmtId="171" formatCode="#,###,##0.000"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00"/>
     <numFmt numFmtId="173" formatCode="#,##0.00"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00"/>
-    <numFmt numFmtId="175" formatCode="#,##0.0"/>
-    <numFmt numFmtId="176" formatCode="#0"/>
-    <numFmt numFmtId="177" formatCode="0%"/>
-    <numFmt numFmtId="178" formatCode="0&quot;%&quot;"/>
-    <numFmt numFmtId="179" formatCode="#,###,###"/>
-    <numFmt numFmtId="180" formatCode="$#,##0"/>
+    <numFmt numFmtId="174" formatCode="#,##0.0"/>
+    <numFmt numFmtId="175" formatCode="#0"/>
+    <numFmt numFmtId="176" formatCode="0%"/>
+    <numFmt numFmtId="177" formatCode="0&quot;%&quot;"/>
+    <numFmt numFmtId="178" formatCode="#,###,###"/>
+    <numFmt numFmtId="179" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -5310,8 +5310,9 @@
     <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -5321,7 +5322,6 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
